--- a/Elevator_All_Models_DB_FULLDATA_v06.xlsx
+++ b/Elevator_All_Models_DB_FULLDATA_v06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1245"/>
+  <dimension ref="A1:G1267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41517,6 +41517,732 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1246" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1247" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1248" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1249" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1250" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1251" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1252" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1253" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1254" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1255" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1256" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1257" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1258" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1259" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1260" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1261" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1262" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1263" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1264" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1265" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1266" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1267" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
